--- a/outputs/daily/hr_rankings_2026-08-11.xlsx
+++ b/outputs/daily/hr_rankings_2026-08-11.xlsx
@@ -11149,27 +11149,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>691023</t>
+          <t>691718</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Walker</t>
+          <t>Pete Crow-Armstrong</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>CHC</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>WSH</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-11T22:45:00Z</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -11179,26 +11179,14 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Cristopher Sánchez</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>650911</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>L</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
       <c r="L34" t="n">
-        <v>55.9</v>
+        <v>55.8</v>
       </c>
       <c r="M34" t="inlineStr">
         <is>
@@ -11212,33 +11200,31 @@
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>55.6</v>
+        <v>54.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>33.3</v>
+        <v>41.2</v>
       </c>
       <c r="R34" t="n">
-        <v>51.1</v>
+        <v>44.7</v>
       </c>
       <c r="S34" t="n">
-        <v>95.5</v>
+        <v>88.7</v>
       </c>
       <c r="T34" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="U34" t="n">
-        <v>51.9</v>
+        <v>70.40000000000001</v>
       </c>
       <c r="V34" t="n">
-        <v>32.9</v>
-      </c>
-      <c r="W34" t="n">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>No</t>
@@ -11251,7 +11237,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -11276,7 +11262,7 @@
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:2026/2025</t>
+          <t>H:2026/2025 P:</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr"/>
@@ -11293,132 +11279,108 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AL34" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Contact streak: 11/32 over last 7 games</t>
+          <t>Hot streak: 2 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN34" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>EV profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
-          <t>12.58</t>
+          <t>12.54</t>
         </is>
       </c>
       <c r="AQ34" t="inlineStr">
         <is>
-          <t>48.32</t>
+          <t>47.06</t>
         </is>
       </c>
       <c r="AR34" t="inlineStr">
         <is>
-          <t>92.58</t>
+          <t>90.06</t>
         </is>
       </c>
       <c r="AS34" t="inlineStr">
         <is>
-          <t>104.7741</t>
+          <t>101.6338</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr">
         <is>
-          <t>0.4498</t>
+          <t>0.4729</t>
         </is>
       </c>
       <c r="AU34" t="inlineStr">
         <is>
-          <t>0.1942</t>
+          <t>0.2211</t>
         </is>
       </c>
       <c r="AV34" t="inlineStr">
         <is>
-          <t>0.3319</t>
+          <t>0.3518</t>
         </is>
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>78.87</t>
+          <t>74.1</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>83.05</t>
+          <t>43.13</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
-          <t>38.59</t>
+          <t>49.67</t>
         </is>
       </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>23.42</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
-          <t>17.9</t>
+          <t>27.5</t>
         </is>
       </c>
       <c r="BB34" t="inlineStr">
         <is>
-          <t>0.1708</t>
-        </is>
-      </c>
-      <c r="BC34" t="inlineStr">
-        <is>
-          <t>7.17</t>
-        </is>
-      </c>
-      <c r="BD34" t="inlineStr">
-        <is>
-          <t>41.83</t>
-        </is>
-      </c>
-      <c r="BE34" t="inlineStr">
-        <is>
-          <t>89.28</t>
-        </is>
-      </c>
-      <c r="BF34" t="inlineStr">
-        <is>
-          <t>0.3569</t>
-        </is>
-      </c>
-      <c r="BG34" t="inlineStr">
-        <is>
-          <t>0.1242</t>
-        </is>
-      </c>
-      <c r="BH34" t="inlineStr">
-        <is>
-          <t>16.97</t>
-        </is>
-      </c>
+          <t>0.2508</t>
+        </is>
+      </c>
+      <c r="BC34" t="inlineStr"/>
+      <c r="BD34" t="inlineStr"/>
+      <c r="BE34" t="inlineStr"/>
+      <c r="BF34" t="inlineStr"/>
+      <c r="BG34" t="inlineStr"/>
+      <c r="BH34" t="inlineStr"/>
       <c r="BI34" t="inlineStr">
         <is>
-          <t>143 deg</t>
+          <t>278 deg</t>
         </is>
       </c>
       <c r="BJ34" t="inlineStr">
@@ -11428,80 +11390,40 @@
       </c>
       <c r="BK34" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.8730&amp;lon=-77.0074</t>
         </is>
       </c>
       <c r="BL34" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BM34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="BN34" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>72</t>
         </is>
       </c>
       <c r="BO34" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Nationals Park</t>
         </is>
       </c>
       <c r="BP34" t="inlineStr"/>
-      <c r="BQ34" t="inlineStr">
-        <is>
-          <t>10.9</t>
-        </is>
-      </c>
-      <c r="BR34" t="inlineStr">
-        <is>
-          <t>0.144</t>
-        </is>
-      </c>
-      <c r="BS34" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="BT34" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="BU34" t="inlineStr">
-        <is>
-          <t>264</t>
-        </is>
-      </c>
-      <c r="BV34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BX34" t="inlineStr">
-        <is>
-          <t>7.62</t>
-        </is>
-      </c>
-      <c r="BY34" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BZ34" t="inlineStr">
-        <is>
-          <t>Volume support but ISO modest</t>
-        </is>
-      </c>
+      <c r="BQ34" t="inlineStr"/>
+      <c r="BR34" t="inlineStr"/>
+      <c r="BS34" t="inlineStr"/>
+      <c r="BT34" t="inlineStr"/>
+      <c r="BU34" t="inlineStr"/>
+      <c r="BV34" t="inlineStr"/>
+      <c r="BW34" t="inlineStr"/>
+      <c r="BX34" t="inlineStr"/>
+      <c r="BY34" t="inlineStr"/>
+      <c r="BZ34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -11509,27 +11431,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>691718</t>
+          <t>665052</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pete Crow-Armstrong</t>
+          <t>Griffin Conine</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CHC</t>
+          <t>MIA</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>WSH</t>
+          <t>PIT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-11T22:45:00Z</t>
+          <t>2026-08-11T22:40:00Z</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -11539,14 +11461,26 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Paul Skenes</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>694973</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
       <c r="L35" t="n">
-        <v>55.8</v>
+        <v>55.7</v>
       </c>
       <c r="M35" t="inlineStr">
         <is>
@@ -11560,26 +11494,26 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>54.1</v>
+        <v>59.7</v>
       </c>
       <c r="Q35" t="n">
-        <v>41.2</v>
+        <v>28.6</v>
       </c>
       <c r="R35" t="n">
-        <v>44.7</v>
+        <v>47</v>
       </c>
       <c r="S35" t="n">
-        <v>88.7</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="U35" t="n">
-        <v>70.40000000000001</v>
+        <v>48.7</v>
       </c>
       <c r="V35" t="n">
         <v>50</v>
@@ -11597,7 +11531,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -11622,7 +11556,7 @@
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>H:2026/2025 P:</t>
+          <t>H:2026/2025 P:2026/2025</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr"/>
@@ -11639,12 +11573,12 @@
       </c>
       <c r="AJ35" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AL35" t="inlineStr">
@@ -11659,88 +11593,112 @@
       </c>
       <c r="AN35" t="inlineStr">
         <is>
-          <t>handedness incomplete; pitcher baseline 0.0% barrel, 0.0 HR allowed</t>
+          <t>platoon edge; pitcher baseline 6.7% barrel, 12.4 HR allowed</t>
         </is>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
-          <t>fly-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
-          <t>12.54</t>
+          <t>15.5</t>
         </is>
       </c>
       <c r="AQ35" t="inlineStr">
         <is>
-          <t>47.06</t>
+          <t>52.02</t>
         </is>
       </c>
       <c r="AR35" t="inlineStr">
         <is>
-          <t>90.06</t>
+          <t>91.53</t>
         </is>
       </c>
       <c r="AS35" t="inlineStr">
         <is>
-          <t>101.6338</t>
+          <t>103.5826</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr">
         <is>
-          <t>0.4729</t>
+          <t>0.4698</t>
         </is>
       </c>
       <c r="AU35" t="inlineStr">
         <is>
-          <t>0.2211</t>
+          <t>0.2173</t>
         </is>
       </c>
       <c r="AV35" t="inlineStr">
         <is>
-          <t>0.3518</t>
+          <t>0.3461</t>
         </is>
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>74.1</t>
+          <t>74.26</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>43.13</t>
+          <t>45.16</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>49.67</t>
+          <t>43.51</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>23.06</t>
         </is>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
-          <t>27.5</t>
+          <t>9.0</t>
         </is>
       </c>
       <c r="BB35" t="inlineStr">
         <is>
-          <t>0.2508</t>
-        </is>
-      </c>
-      <c r="BC35" t="inlineStr"/>
-      <c r="BD35" t="inlineStr"/>
-      <c r="BE35" t="inlineStr"/>
-      <c r="BF35" t="inlineStr"/>
-      <c r="BG35" t="inlineStr"/>
-      <c r="BH35" t="inlineStr"/>
+          <t>0.2448</t>
+        </is>
+      </c>
+      <c r="BC35" t="inlineStr">
+        <is>
+          <t>6.71</t>
+        </is>
+      </c>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>39.4</t>
+        </is>
+      </c>
+      <c r="BE35" t="inlineStr">
+        <is>
+          <t>88.16</t>
+        </is>
+      </c>
+      <c r="BF35" t="inlineStr">
+        <is>
+          <t>0.3273</t>
+        </is>
+      </c>
+      <c r="BG35" t="inlineStr">
+        <is>
+          <t>0.1211</t>
+        </is>
+      </c>
+      <c r="BH35" t="inlineStr">
+        <is>
+          <t>24.06</t>
+        </is>
+      </c>
       <c r="BI35" t="inlineStr">
         <is>
-          <t>278 deg</t>
+          <t>83 deg</t>
         </is>
       </c>
       <c r="BJ35" t="inlineStr">
@@ -11750,27 +11708,27 @@
       </c>
       <c r="BK35" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.8730&amp;lon=-77.0074</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=25.7781&amp;lon=-80.2197</t>
         </is>
       </c>
       <c r="BL35" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>81</t>
         </is>
       </c>
       <c r="BM35" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN35" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO35" t="inlineStr">
         <is>
-          <t>Nationals Park</t>
+          <t>loanDepot park</t>
         </is>
       </c>
       <c r="BP35" t="inlineStr"/>
@@ -11791,27 +11749,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>665052</t>
+          <t>641933</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Griffin Conine</t>
+          <t>Tyler O'Neill</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>MIA</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>PIT</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-11T22:40:00Z</t>
+          <t>2026-08-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11826,12 +11784,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Paul Skenes</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>694973</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -11840,7 +11798,7 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>55.7</v>
+        <v>55.4</v>
       </c>
       <c r="M36" t="inlineStr">
         <is>
@@ -11854,31 +11812,33 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
         </is>
       </c>
       <c r="P36" t="n">
-        <v>59.7</v>
+        <v>48.6</v>
       </c>
       <c r="Q36" t="n">
-        <v>28.6</v>
+        <v>50.6</v>
       </c>
       <c r="R36" t="n">
-        <v>47</v>
+        <v>51.6</v>
       </c>
       <c r="S36" t="n">
         <v>90.40000000000001</v>
       </c>
       <c r="T36" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="U36" t="n">
-        <v>48.7</v>
+        <v>78.7</v>
       </c>
       <c r="V36" t="n">
-        <v>50</v>
-      </c>
-      <c r="W36" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="W36" t="n">
+        <v>42</v>
+      </c>
       <c r="X36" t="inlineStr">
         <is>
           <t>No</t>
@@ -11938,127 +11898,127 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>18</t>
         </is>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Hot streak: 2 HR in last 7 games</t>
+          <t>Hot streak: 3 HR in last 7 games</t>
         </is>
       </c>
       <c r="AN36" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 6.7% barrel, 12.4 HR allowed</t>
+          <t>same-side matchup; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>fly-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
-          <t>15.5</t>
+          <t>11.6</t>
         </is>
       </c>
       <c r="AQ36" t="inlineStr">
         <is>
-          <t>52.02</t>
+          <t>40.85</t>
         </is>
       </c>
       <c r="AR36" t="inlineStr">
         <is>
-          <t>91.53</t>
+          <t>89.43</t>
         </is>
       </c>
       <c r="AS36" t="inlineStr">
         <is>
-          <t>103.5826</t>
+          <t>100.3792</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr">
         <is>
-          <t>0.4698</t>
+          <t>0.4404</t>
         </is>
       </c>
       <c r="AU36" t="inlineStr">
         <is>
-          <t>0.2173</t>
+          <t>0.2212</t>
         </is>
       </c>
       <c r="AV36" t="inlineStr">
         <is>
-          <t>0.3461</t>
+          <t>0.325</t>
         </is>
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>74.26</t>
+          <t>72.81</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>45.16</t>
+          <t>23.12</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>45.37</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>23.06</t>
+          <t>39.91</t>
         </is>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
-          <t>9.0</t>
+          <t>9.7</t>
         </is>
       </c>
       <c r="BB36" t="inlineStr">
         <is>
-          <t>0.2448</t>
+          <t>0.1909</t>
         </is>
       </c>
       <c r="BC36" t="inlineStr">
         <is>
-          <t>6.71</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BD36" t="inlineStr">
         <is>
-          <t>39.4</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
-          <t>88.16</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="BF36" t="inlineStr">
         <is>
-          <t>0.3273</t>
+          <t>0.4501</t>
         </is>
       </c>
       <c r="BG36" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>24.06</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="BI36" t="inlineStr">
         <is>
-          <t>83 deg</t>
+          <t>45 deg</t>
         </is>
       </c>
       <c r="BJ36" t="inlineStr">
@@ -12068,12 +12028,12 @@
       </c>
       <c r="BK36" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=25.7781&amp;lon=-80.2197</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL36" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM36" t="inlineStr">
@@ -12088,20 +12048,60 @@
       </c>
       <c r="BO36" t="inlineStr">
         <is>
-          <t>loanDepot park</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP36" t="inlineStr"/>
-      <c r="BQ36" t="inlineStr"/>
-      <c r="BR36" t="inlineStr"/>
-      <c r="BS36" t="inlineStr"/>
-      <c r="BT36" t="inlineStr"/>
-      <c r="BU36" t="inlineStr"/>
-      <c r="BV36" t="inlineStr"/>
-      <c r="BW36" t="inlineStr"/>
-      <c r="BX36" t="inlineStr"/>
-      <c r="BY36" t="inlineStr"/>
-      <c r="BZ36" t="inlineStr"/>
+      <c r="BQ36" t="inlineStr">
+        <is>
+          <t>11.5</t>
+        </is>
+      </c>
+      <c r="BR36" t="inlineStr">
+        <is>
+          <t>0.182</t>
+        </is>
+      </c>
+      <c r="BS36" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BT36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BU36" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="BV36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW36" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="BX36" t="inlineStr">
+        <is>
+          <t>4.84</t>
+        </is>
+      </c>
+      <c r="BY36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="BZ36" t="inlineStr">
+        <is>
+          <t>Moderate profile</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -12109,27 +12109,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>641933</t>
+          <t>691023</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tyler O'Neill</t>
+          <t>Jordan Walker</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-11T23:40:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -12139,22 +12139,22 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L37" t="n">
@@ -12172,32 +12172,32 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Hot Hitter/Streak</t>
+          <t>Projected Lineup, Strong Barrel, Premium Lineup Spot, Platoon Edge</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>48.6</v>
+        <v>55.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>50.6</v>
+        <v>33.3</v>
       </c>
       <c r="R37" t="n">
-        <v>51.6</v>
+        <v>51.1</v>
       </c>
       <c r="S37" t="n">
-        <v>90.40000000000001</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="T37" t="n">
-        <v>50</v>
+        <v>78</v>
       </c>
       <c r="U37" t="n">
-        <v>78.7</v>
+        <v>51.9</v>
       </c>
       <c r="V37" t="n">
-        <v>18</v>
+        <v>32.9</v>
       </c>
       <c r="W37" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -12211,7 +12211,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -12253,188 +12253,188 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AL37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Contact streak: 11/32 over last 7 games</t>
+        </is>
+      </c>
+      <c r="AN37" t="inlineStr">
+        <is>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>EV profile; pitcher fly-ball pressure modest</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>12.58</t>
+        </is>
+      </c>
+      <c r="AQ37" t="inlineStr">
+        <is>
+          <t>48.32</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>92.58</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr">
+        <is>
+          <t>104.7741</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr">
+        <is>
+          <t>0.4498</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>0.1942</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>0.3319</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>78.87</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>83.05</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>38.59</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>23.42</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>17.9</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>0.1708</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>7.17</t>
+        </is>
+      </c>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>41.83</t>
+        </is>
+      </c>
+      <c r="BE37" t="inlineStr">
+        <is>
+          <t>89.28</t>
+        </is>
+      </c>
+      <c r="BF37" t="inlineStr">
+        <is>
+          <t>0.3569</t>
+        </is>
+      </c>
+      <c r="BG37" t="inlineStr">
+        <is>
+          <t>0.1242</t>
+        </is>
+      </c>
+      <c r="BH37" t="inlineStr">
+        <is>
+          <t>16.97</t>
+        </is>
+      </c>
+      <c r="BI37" t="inlineStr">
+        <is>
+          <t>143 deg</t>
+        </is>
+      </c>
+      <c r="BJ37" t="inlineStr">
+        <is>
+          <t>Open-Meteo forecast; MLB fallback</t>
+        </is>
+      </c>
+      <c r="BK37" t="inlineStr">
+        <is>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+        </is>
+      </c>
+      <c r="BL37" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="BM37" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AL37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Hot streak: 3 HR in last 7 games</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>same-side matchup; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>fly-ball profile; pitcher allows elevated contact</t>
-        </is>
-      </c>
-      <c r="AP37" t="inlineStr">
-        <is>
-          <t>11.6</t>
-        </is>
-      </c>
-      <c r="AQ37" t="inlineStr">
-        <is>
-          <t>40.85</t>
-        </is>
-      </c>
-      <c r="AR37" t="inlineStr">
-        <is>
-          <t>89.43</t>
-        </is>
-      </c>
-      <c r="AS37" t="inlineStr">
-        <is>
-          <t>100.3792</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr">
-        <is>
-          <t>0.4404</t>
-        </is>
-      </c>
-      <c r="AU37" t="inlineStr">
-        <is>
-          <t>0.2212</t>
-        </is>
-      </c>
-      <c r="AV37" t="inlineStr">
-        <is>
-          <t>0.325</t>
-        </is>
-      </c>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>72.81</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>23.12</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>45.37</t>
-        </is>
-      </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>39.91</t>
-        </is>
-      </c>
-      <c r="BA37" t="inlineStr">
-        <is>
-          <t>9.7</t>
-        </is>
-      </c>
-      <c r="BB37" t="inlineStr">
-        <is>
-          <t>0.1909</t>
-        </is>
-      </c>
-      <c r="BC37" t="inlineStr">
-        <is>
-          <t>10.06</t>
-        </is>
-      </c>
-      <c r="BD37" t="inlineStr">
-        <is>
-          <t>34.9</t>
-        </is>
-      </c>
-      <c r="BE37" t="inlineStr">
-        <is>
-          <t>88.62</t>
-        </is>
-      </c>
-      <c r="BF37" t="inlineStr">
-        <is>
-          <t>0.4501</t>
-        </is>
-      </c>
-      <c r="BG37" t="inlineStr">
-        <is>
-          <t>0.2</t>
-        </is>
-      </c>
-      <c r="BH37" t="inlineStr">
-        <is>
-          <t>31.06</t>
-        </is>
-      </c>
-      <c r="BI37" t="inlineStr">
-        <is>
-          <t>45 deg</t>
-        </is>
-      </c>
-      <c r="BJ37" t="inlineStr">
-        <is>
-          <t>Open-Meteo forecast; MLB fallback</t>
-        </is>
-      </c>
-      <c r="BK37" t="inlineStr">
-        <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
-        </is>
-      </c>
-      <c r="BL37" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="BM37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BN37" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BO37" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BP37" t="inlineStr"/>
       <c r="BQ37" t="inlineStr">
         <is>
-          <t>11.5</t>
+          <t>10.9</t>
         </is>
       </c>
       <c r="BR37" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>0.144</t>
         </is>
       </c>
       <c r="BS37" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BT37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>9</t>
         </is>
       </c>
       <c r="BU37" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>264</t>
         </is>
       </c>
       <c r="BV37" t="inlineStr">
@@ -12444,22 +12444,22 @@
       </c>
       <c r="BW37" t="inlineStr">
         <is>
-          <t>-4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BX37" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>7.62</t>
         </is>
       </c>
       <c r="BY37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BZ37" t="inlineStr">
         <is>
-          <t>Moderate profile</t>
+          <t>Volume support but ISO modest</t>
         </is>
       </c>
     </row>
@@ -25901,27 +25901,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>673357</t>
+          <t>671056</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Luis Robert</t>
+          <t>Ivan Herrera</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NYM</t>
+          <t>STL</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>ATL</t>
+          <t>PHI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-11T23:15:00Z</t>
+          <t>2026-08-11T23:45:00Z</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -25931,17 +25931,17 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Martín Pérez</t>
+          <t>Cristopher Sánchez</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>527048</t>
+          <t>650911</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -25950,7 +25950,7 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>50.3</v>
+        <v>50.6</v>
       </c>
       <c r="M80" t="inlineStr">
         <is>
@@ -25968,22 +25968,22 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>32.3</v>
+        <v>34.9</v>
       </c>
       <c r="Q80" t="n">
-        <v>39.5</v>
+        <v>33.3</v>
       </c>
       <c r="R80" t="n">
-        <v>53.9</v>
+        <v>51.1</v>
       </c>
       <c r="S80" t="n">
-        <v>90.40000000000001</v>
+        <v>95.5</v>
       </c>
       <c r="T80" t="n">
         <v>78</v>
       </c>
       <c r="U80" t="n">
-        <v>44.1</v>
+        <v>58.4</v>
       </c>
       <c r="V80" t="n">
         <v>50</v>
@@ -26001,7 +26001,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -26043,12 +26043,12 @@
       </c>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>31</t>
         </is>
       </c>
       <c r="AL80" t="inlineStr">
@@ -26058,12 +26058,12 @@
       </c>
       <c r="AM80" t="inlineStr">
         <is>
-          <t>Last 7 games: 7/24, 1 HR</t>
+          <t>Contact streak: 12/31 over last 7 games</t>
         </is>
       </c>
       <c r="AN80" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 8.6% barrel, 9.5 HR allowed</t>
+          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
         </is>
       </c>
       <c r="AO80" t="inlineStr">
@@ -26073,102 +26073,102 @@
       </c>
       <c r="AP80" t="inlineStr">
         <is>
-          <t>6.45</t>
+          <t>7.25</t>
         </is>
       </c>
       <c r="AQ80" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>43.22</t>
         </is>
       </c>
       <c r="AR80" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>90.08</t>
         </is>
       </c>
       <c r="AS80" t="inlineStr">
         <is>
-          <t>101.5476</t>
+          <t>101.478</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr">
         <is>
-          <t>0.3819</t>
+          <t>0.4107</t>
         </is>
       </c>
       <c r="AU80" t="inlineStr">
         <is>
-          <t>0.1506</t>
+          <t>0.1541</t>
         </is>
       </c>
       <c r="AV80" t="inlineStr">
         <is>
-          <t>0.3028</t>
+          <t>0.3421</t>
         </is>
       </c>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>73.95</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>43.77</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>37.8</t>
         </is>
       </c>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>26.75</t>
+          <t>18.89</t>
         </is>
       </c>
       <c r="BA80" t="inlineStr">
         <is>
-          <t>7.7</t>
+          <t>14.8</t>
         </is>
       </c>
       <c r="BB80" t="inlineStr">
         <is>
-          <t>0.1312</t>
+          <t>0.1548</t>
         </is>
       </c>
       <c r="BC80" t="inlineStr">
         <is>
-          <t>8.63</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="BD80" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>41.83</t>
         </is>
       </c>
       <c r="BE80" t="inlineStr">
         <is>
-          <t>88.06</t>
+          <t>89.28</t>
         </is>
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>0.4185</t>
+          <t>0.3569</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>0.1674</t>
+          <t>0.1242</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>16.97</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>228 deg</t>
+          <t>143 deg</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr">
@@ -26178,27 +26178,27 @@
       </c>
       <c r="BK80" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
         </is>
       </c>
       <c r="BL80" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="BM80" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="BN80" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>91</t>
         </is>
       </c>
       <c r="BO80" t="inlineStr">
         <is>
-          <t>Truist Park</t>
+          <t>Busch Stadium</t>
         </is>
       </c>
       <c r="BP80" t="inlineStr"/>
@@ -26219,27 +26219,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>702616</t>
+          <t>673357</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jackson Holliday</t>
+          <t>Luis Robert</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>BAL</t>
+          <t>NYM</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MIN</t>
+          <t>ATL</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-11T23:40:00Z</t>
+          <t>2026-08-11T23:15:00Z</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -26249,22 +26249,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Bailey Ober</t>
+          <t>Martín Pérez</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>641927</t>
+          <t>527048</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>L</t>
         </is>
       </c>
       <c r="L81" t="n">
@@ -26286,29 +26286,27 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>28.5</v>
+        <v>32.3</v>
       </c>
       <c r="Q81" t="n">
-        <v>50.6</v>
+        <v>39.5</v>
       </c>
       <c r="R81" t="n">
-        <v>51.6</v>
+        <v>53.9</v>
       </c>
       <c r="S81" t="n">
-        <v>92.09999999999999</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="T81" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="U81" t="n">
-        <v>37.8</v>
+        <v>44.1</v>
       </c>
       <c r="V81" t="n">
-        <v>28.9</v>
-      </c>
-      <c r="W81" t="n">
-        <v>55</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="W81" t="inlineStr"/>
       <c r="X81" t="inlineStr">
         <is>
           <t>No</t>
@@ -26321,7 +26319,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -26363,7 +26361,7 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -26378,117 +26376,117 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Last 7 games: 6/24, 1 HR</t>
+          <t>Last 7 games: 7/24, 1 HR</t>
         </is>
       </c>
       <c r="AN81" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
+          <t>platoon edge; pitcher baseline 8.6% barrel, 9.5 HR allowed</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
+          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
         </is>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
-          <t>8.01</t>
+          <t>6.45</t>
         </is>
       </c>
       <c r="AQ81" t="inlineStr">
         <is>
-          <t>38.0</t>
+          <t>39.43</t>
         </is>
       </c>
       <c r="AR81" t="inlineStr">
         <is>
-          <t>87.75</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AS81" t="inlineStr">
         <is>
-          <t>98.3612</t>
+          <t>101.5476</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>0.3819</t>
         </is>
       </c>
       <c r="AU81" t="inlineStr">
         <is>
-          <t>0.1448</t>
+          <t>0.1506</t>
         </is>
       </c>
       <c r="AV81" t="inlineStr">
         <is>
-          <t>0.3182</t>
+          <t>0.3028</t>
         </is>
       </c>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>70.6</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>7.69</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr">
         <is>
-          <t>36.39</t>
+          <t>46.93</t>
         </is>
       </c>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>25.52</t>
+          <t>26.75</t>
         </is>
       </c>
       <c r="BA81" t="inlineStr">
         <is>
-          <t>9.3</t>
+          <t>7.7</t>
         </is>
       </c>
       <c r="BB81" t="inlineStr">
         <is>
-          <t>0.1414</t>
+          <t>0.1312</t>
         </is>
       </c>
       <c r="BC81" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>8.63</t>
         </is>
       </c>
       <c r="BD81" t="inlineStr">
         <is>
-          <t>34.9</t>
+          <t>37.65</t>
         </is>
       </c>
       <c r="BE81" t="inlineStr">
         <is>
-          <t>88.62</t>
+          <t>88.06</t>
         </is>
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>0.4501</t>
+          <t>0.4185</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1674</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>31.06</t>
+          <t>24.48</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>45 deg</t>
+          <t>228 deg</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr">
@@ -26498,80 +26496,40 @@
       </c>
       <c r="BK81" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=33.8907&amp;lon=-84.4677</t>
         </is>
       </c>
       <c r="BL81" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>68</t>
         </is>
       </c>
       <c r="BM81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="BN81" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>85</t>
         </is>
       </c>
       <c r="BO81" t="inlineStr">
         <is>
-          <t>Target Field</t>
+          <t>Truist Park</t>
         </is>
       </c>
       <c r="BP81" t="inlineStr"/>
-      <c r="BQ81" t="inlineStr">
-        <is>
-          <t>13.0</t>
-        </is>
-      </c>
-      <c r="BR81" t="inlineStr">
-        <is>
-          <t>0.227</t>
-        </is>
-      </c>
-      <c r="BS81" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="BT81" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="BU81" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="BV81" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BW81" t="inlineStr">
-        <is>
-          <t>-4</t>
-        </is>
-      </c>
-      <c r="BX81" t="inlineStr">
-        <is>
-          <t>5.43</t>
-        </is>
-      </c>
-      <c r="BY81" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="BZ81" t="inlineStr">
-        <is>
-          <t>Best BAL full sheet line but park neutral-negative</t>
-        </is>
-      </c>
+      <c r="BQ81" t="inlineStr"/>
+      <c r="BR81" t="inlineStr"/>
+      <c r="BS81" t="inlineStr"/>
+      <c r="BT81" t="inlineStr"/>
+      <c r="BU81" t="inlineStr"/>
+      <c r="BV81" t="inlineStr"/>
+      <c r="BW81" t="inlineStr"/>
+      <c r="BX81" t="inlineStr"/>
+      <c r="BY81" t="inlineStr"/>
+      <c r="BZ81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -26579,27 +26537,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>671056</t>
+          <t>702616</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ivan Herrera</t>
+          <t>Jackson Holliday</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>STL</t>
+          <t>BAL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PHI</t>
+          <t>MIN</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-11T23:45:00Z</t>
+          <t>2026-08-11T23:40:00Z</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -26614,21 +26572,21 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Cristopher Sánchez</t>
+          <t>Bailey Ober</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>650911</t>
+          <t>641927</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>L</t>
+          <t>R</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="M82" t="inlineStr">
         <is>
@@ -26646,27 +26604,29 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>34.9</v>
+        <v>28.5</v>
       </c>
       <c r="Q82" t="n">
-        <v>33.3</v>
+        <v>50.6</v>
       </c>
       <c r="R82" t="n">
-        <v>51.1</v>
+        <v>51.6</v>
       </c>
       <c r="S82" t="n">
         <v>92.09999999999999</v>
       </c>
       <c r="T82" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="U82" t="n">
-        <v>58.4</v>
+        <v>37.8</v>
       </c>
       <c r="V82" t="n">
-        <v>50</v>
-      </c>
-      <c r="W82" t="inlineStr"/>
+        <v>28.9</v>
+      </c>
+      <c r="W82" t="n">
+        <v>55</v>
+      </c>
       <c r="X82" t="inlineStr">
         <is>
           <t>No</t>
@@ -26721,12 +26681,12 @@
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AL82" t="inlineStr">
@@ -26736,117 +26696,117 @@
       </c>
       <c r="AM82" t="inlineStr">
         <is>
-          <t>Contact streak: 12/31 over last 7 games</t>
+          <t>Last 7 games: 6/24, 1 HR</t>
         </is>
       </c>
       <c r="AN82" t="inlineStr">
         <is>
-          <t>platoon edge; pitcher baseline 7.2% barrel, 12.7 HR allowed</t>
+          <t>platoon edge; pitcher baseline 10.1% barrel, 18.8 HR allowed</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>neutral batted-ball profile; pitcher fly-ball pressure modest</t>
+          <t>neutral batted-ball profile; pitcher allows elevated contact</t>
         </is>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
-          <t>7.25</t>
+          <t>8.01</t>
         </is>
       </c>
       <c r="AQ82" t="inlineStr">
         <is>
-          <t>43.22</t>
+          <t>38.0</t>
         </is>
       </c>
       <c r="AR82" t="inlineStr">
         <is>
-          <t>90.08</t>
+          <t>87.75</t>
         </is>
       </c>
       <c r="AS82" t="inlineStr">
         <is>
-          <t>101.478</t>
+          <t>98.3612</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr">
         <is>
-          <t>0.4107</t>
+          <t>0.383</t>
         </is>
       </c>
       <c r="AU82" t="inlineStr">
         <is>
-          <t>0.1541</t>
+          <t>0.1448</t>
         </is>
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>0.3421</t>
+          <t>0.3182</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>73.95</t>
+          <t>70.6</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>7.69</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>37.8</t>
+          <t>36.39</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>25.52</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>14.8</t>
+          <t>9.3</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>0.1548</t>
+          <t>0.1414</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BD82" t="inlineStr">
         <is>
-          <t>41.83</t>
+          <t>34.9</t>
         </is>
       </c>
       <c r="BE82" t="inlineStr">
         <is>
-          <t>89.28</t>
+          <t>88.62</t>
         </is>
       </c>
       <c r="BF82" t="inlineStr">
         <is>
-          <t>0.3569</t>
+          <t>0.4501</t>
         </is>
       </c>
       <c r="BG82" t="inlineStr">
         <is>
-          <t>0.1242</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>31.06</t>
         </is>
       </c>
       <c r="BI82" t="inlineStr">
         <is>
-          <t>143 deg</t>
+          <t>45 deg</t>
         </is>
       </c>
       <c r="BJ82" t="inlineStr">
@@ -26856,40 +26816,80 @@
       </c>
       <c r="BK82" t="inlineStr">
         <is>
-          <t>https://forecast.weather.gov/MapClick.php?lat=38.6226&amp;lon=-90.1928</t>
+          <t>https://forecast.weather.gov/MapClick.php?lat=44.9817&amp;lon=-93.2776</t>
         </is>
       </c>
       <c r="BL82" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>47</t>
         </is>
       </c>
       <c r="BM82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN82" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>84</t>
         </is>
       </c>
       <c r="BO82" t="inlineStr">
         <is>
-          <t>Busch Stadium</t>
+          <t>Target Field</t>
         </is>
       </c>
       <c r="BP82" t="inlineStr"/>
-      <c r="BQ82" t="inlineStr"/>
-      <c r="BR82" t="inlineStr"/>
-      <c r="BS82" t="inlineStr"/>
-      <c r="BT82" t="inlineStr"/>
-      <c r="BU82" t="inlineStr"/>
-      <c r="BV82" t="inlineStr"/>
-      <c r="BW82" t="inlineStr"/>
-      <c r="BX82" t="inlineStr"/>
-      <c r="BY82" t="inlineStr"/>
-      <c r="BZ82" t="inlineStr"/>
+      <c r="BQ82" t="inlineStr">
+        <is>
+          <t>13.0</t>
+        </is>
+      </c>
+      <c r="BR82" t="inlineStr">
+        <is>
+          <t>0.227</t>
+        </is>
+      </c>
+      <c r="BS82" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="BT82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="BU82" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="BV82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BW82" t="inlineStr">
+        <is>
+          <t>-4</t>
+        </is>
+      </c>
+      <c r="BX82" t="inlineStr">
+        <is>
+          <t>5.43</t>
+        </is>
+      </c>
+      <c r="BY82" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="BZ82" t="inlineStr">
+        <is>
+          <t>Best BAL full sheet line but park neutral-negative</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
